--- a/Stock_Portfolio_Manager.xlsx
+++ b/Stock_Portfolio_Manager.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarah\Documents\05. Programmieren (29.05.2025)\02. Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E2859C-6F77-4867-A3F5-61CD5A57A6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DDD767-A94E-4622-BA5C-528587FF23A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{7FF362F3-F34D-4D23-9DD2-08D48BDB709E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7FF362F3-F34D-4D23-9DD2-08D48BDB709E}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="3" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="50">
   <si>
     <t>Datum</t>
   </si>
@@ -128,9 +128,6 @@
     <t>Portfolio</t>
   </si>
   <si>
-    <t>Wert</t>
-  </si>
-  <si>
     <t>Positionen</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>LU0340285161</t>
   </si>
   <si>
-    <t>Kaufpreis</t>
-  </si>
-  <si>
     <t>Durchschn. Preis p. S.</t>
   </si>
   <si>
@@ -150,9 +144,6 @@
   </si>
   <si>
     <t>Position</t>
-  </si>
-  <si>
-    <t>Aktueller Wert p. S.</t>
   </si>
   <si>
     <t>Column1</t>
@@ -243,6 +234,18 @@
   <si>
     <t>0,00</t>
   </si>
+  <si>
+    <t>Aktueller Wert</t>
+  </si>
+  <si>
+    <t>Aktueller Wert p. S. (€)</t>
+  </si>
+  <si>
+    <t>Gewinn</t>
+  </si>
+  <si>
+    <t>Dividende gesamt</t>
+  </si>
 </sst>
 </file>
 
@@ -252,7 +255,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-407]_-;\-* #,##0.00\ [$€-407]_-;_-* &quot;-&quot;??\ [$€-407]_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +280,59 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="6"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -574,7 +630,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -613,10 +669,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1"/>
@@ -630,14 +683,371 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="43">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1421,7 +1831,409 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Anteile</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Portfolio!$L$6:$L$21</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>A0NCFR</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ETF903</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>DBX0TR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-8AF8-46D7-B786-F9511F549654}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-8AF8-46D7-B786-F9511F549654}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-8AF8-46D7-B786-F9511F549654}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Portfolio!$L$6:$L$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Portfolio!$L$6:$L$8</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>A0NCFR</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ETF903</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>DBX0TR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Portfolio!$N$6:$N$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Portfolio!$N$6:$N$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.42420613706832033</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.47402972308350266</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10176413984817706</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:categoryFilterExceptions/>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8AF8-46D7-B786-F9511F549654}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1945,6 +2757,525 @@
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2015,6 +3346,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>19539</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>172104</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>178038</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF2F7B6-C77D-50E8-D2EB-BD28A3634943}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2046,9 +3413,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{ACE19090-2905-4952-8C7B-D72F5C07F184}" name="Realtime_Kurse_UBS_ETF_MSCI_WORLD_" displayName="Realtime_Kurse_UBS_ETF_MSCI_WORLD_" ref="A1:C5" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:C5" xr:uid="{ACE19090-2905-4952-8C7B-D72F5C07F184}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{AD04E943-DFA5-4AA8-80F0-EC301BFDF391}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{97BD2EB0-1DA9-4691-94C4-3C9CEEDE7C5F}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{94A8EAFF-5B00-4344-BAD1-F590259F0A6C}" uniqueName="3" name="Column3" queryTableFieldId="3" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{AD04E943-DFA5-4AA8-80F0-EC301BFDF391}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{97BD2EB0-1DA9-4691-94C4-3C9CEEDE7C5F}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{94A8EAFF-5B00-4344-BAD1-F590259F0A6C}" uniqueName="3" name="Column3" queryTableFieldId="3" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2070,9 +3437,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FD1C5DA-24E0-4949-8E7A-F755AB028C08}" name="Realtime_Kurse_Lyxor_1_DivDax_UCITS_ETF__I" displayName="Realtime_Kurse_Lyxor_1_DivDax_UCITS_ETF__I" ref="A1:C5" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:C5" xr:uid="{5FD1C5DA-24E0-4949-8E7A-F755AB028C08}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FAE67247-FFC1-4EC8-830E-33D262040965}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{76FF8DD9-503A-4314-84ED-FE1E72493681}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{04ECDD48-E9D7-4E1D-B3ED-642D087570CD}" uniqueName="3" name="Column3" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{FAE67247-FFC1-4EC8-830E-33D262040965}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{76FF8DD9-503A-4314-84ED-FE1E72493681}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{04ECDD48-E9D7-4E1D-B3ED-642D087570CD}" uniqueName="3" name="Column3" queryTableFieldId="3" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2395,19 +3762,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C0476F-1494-427E-8F63-86EF89080B2C}">
-  <dimension ref="B1:AB40"/>
+  <dimension ref="B1:AB26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="2.81640625" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.81640625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2.81640625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="2.81640625" customWidth="1"/>
     <col min="11" max="11" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="2.81640625" customWidth="1"/>
-    <col min="13" max="13" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="2.81640625" customWidth="1"/>
     <col min="15" max="15" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="16" max="18" width="2.81640625" customWidth="1"/>
@@ -2458,7 +3825,7 @@
       <c r="H3" s="6"/>
       <c r="J3" s="4"/>
       <c r="K3" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -2513,15 +3880,15 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="35" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="35" t="s">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="H5" s="6"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="49" t="s">
         <v>5</v>
       </c>
       <c r="L5" s="5"/>
@@ -2530,31 +3897,31 @@
       <c r="O5" s="5"/>
       <c r="P5" s="6"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="T5" s="49">
+      <c r="S5" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="T5" s="46">
         <v>2022</v>
       </c>
-      <c r="U5" s="49">
+      <c r="U5" s="46">
         <v>2023</v>
       </c>
-      <c r="V5" s="49">
+      <c r="V5" s="46">
         <v>2024</v>
       </c>
-      <c r="W5" s="49">
+      <c r="W5" s="46">
         <v>2025</v>
       </c>
-      <c r="X5" s="49">
+      <c r="X5" s="46">
         <v>2026</v>
       </c>
-      <c r="Y5" s="49">
+      <c r="Y5" s="46">
         <v>2027</v>
       </c>
-      <c r="Z5" s="49">
+      <c r="Z5" s="46">
         <v>2028</v>
       </c>
-      <c r="AA5" s="50">
+      <c r="AA5" s="47">
         <v>2029</v>
       </c>
       <c r="AB5" s="6"/>
@@ -2563,10 +3930,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="22">
         <f>-SUM(Transaktionen!G6:G21)</f>
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="37">
+      <c r="E6" s="36">
         <f>M8+M14+M20</f>
         <v>9353</v>
       </c>
@@ -2584,8 +3951,8 @@
       <c r="O6" s="5"/>
       <c r="P6" s="6"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="35" t="s">
-        <v>22</v>
+      <c r="S6" s="52" t="s">
+        <v>20</v>
       </c>
       <c r="T6" s="33" cm="1">
         <f t="array" ref="T6">SUMPRODUCT(--(YEAR(Transaktionen!$K$6:$K$21)=Dashboard!T$5),Transaktionen!$M$6:$M$21)</f>
@@ -2627,12 +3994,12 @@
       <c r="D7" s="5"/>
       <c r="E7" s="30">
         <f>E6/C6</f>
-        <v>2.3382499999999999</v>
+        <v>2.0784444444444445</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="30">
         <f>G6/C6</f>
-        <v>0.02</v>
+        <v>1.7777777777777778E-2</v>
       </c>
       <c r="H7" s="6"/>
       <c r="J7" s="4"/>
@@ -2641,7 +4008,7 @@
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="35" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="35" t="s">
@@ -2649,7 +4016,7 @@
       </c>
       <c r="P7" s="6"/>
       <c r="R7" s="4"/>
-      <c r="S7" s="36" t="s">
+      <c r="S7" s="53" t="s">
         <v>5</v>
       </c>
       <c r="T7" s="31" cm="1">
@@ -2690,9 +4057,8 @@
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="40">
-        <f>E6-C6</f>
-        <v>5353</v>
+      <c r="E8" s="24" t="s">
+        <v>48</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -2703,8 +4069,8 @@
         <v>1000</v>
       </c>
       <c r="L8" s="5"/>
-      <c r="M8" s="37">
-        <f>_xlfn.XLOOKUP(K5,Portfolio!$D$6:$D$21,Portfolio!$F$6:$F$21)*_xlfn.XLOOKUP(K5,Portfolio!$D$6:$D$21,Portfolio!$I$6:$I$21)</f>
+      <c r="M8" s="36">
+        <f>_xlfn.XLOOKUP(K5,Portfolio!$D$6:$D$21,Portfolio!$F$6:$F$21)*_xlfn.XLOOKUP(K5,Portfolio!$D$6:$D$21,Portfolio!$H$6:$H$21)</f>
         <v>3967.6</v>
       </c>
       <c r="N8" s="7"/>
@@ -2714,7 +4080,7 @@
       </c>
       <c r="P8" s="6"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="36" t="s">
+      <c r="S8" s="54" t="s">
         <v>6</v>
       </c>
       <c r="T8" s="31" cm="1">
@@ -2751,14 +4117,17 @@
       </c>
       <c r="AB8" s="6"/>
     </row>
-    <row r="9" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="37">
+        <f>E6-C6</f>
+        <v>4853</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="6"/>
       <c r="J9" s="4"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -2773,8 +4142,8 @@
       </c>
       <c r="P9" s="6"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="51" t="s">
-        <v>32</v>
+      <c r="S9" s="55" t="s">
+        <v>29</v>
       </c>
       <c r="T9" s="32" cm="1">
         <f t="array" ref="T9">SUMPRODUCT(--(YEAR(Transaktionen!$K$6:$K$21)=Dashboard!T$5),Transaktionen!$M$6:$M$21,--(Transaktionen!$L$6:$L$21=$S9))</f>
@@ -2811,6 +4180,13 @@
       <c r="AB9" s="6"/>
     </row>
     <row r="10" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="6"/>
       <c r="J10" s="4"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -2831,9 +4207,15 @@
       <c r="AB10" s="6"/>
     </row>
     <row r="11" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="C11" s="39"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="6"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="50" t="s">
         <v>6</v>
       </c>
       <c r="L11" s="5"/>
@@ -2854,6 +4236,13 @@
       <c r="AB11" s="6"/>
     </row>
     <row r="12" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="6"/>
       <c r="J12" s="4"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
@@ -2874,13 +4263,20 @@
       <c r="AB12" s="6"/>
     </row>
     <row r="13" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="6"/>
       <c r="J13" s="4"/>
       <c r="K13" s="35" t="s">
         <v>14</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="35" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="35" t="s">
@@ -2900,14 +4296,21 @@
       <c r="AB13" s="6"/>
     </row>
     <row r="14" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="6"/>
       <c r="J14" s="4"/>
       <c r="K14" s="22">
         <f>-SUMIF(Transaktionen!$D$6:$D$21,Dashboard!K11,Transaktionen!$G$6:$G$21)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="L14" s="5"/>
-      <c r="M14" s="37">
-        <f>_xlfn.XLOOKUP(K11,Portfolio!$D$6:$D$21,Portfolio!$F$6:$F$21)*_xlfn.XLOOKUP(K11,Portfolio!$D$6:$D$21,Portfolio!$I$6:$I$21)</f>
+      <c r="M14" s="36">
+        <f>_xlfn.XLOOKUP(K11,Portfolio!$D$6:$D$21,Portfolio!$F$6:$F$21)*_xlfn.XLOOKUP(K11,Portfolio!$D$6:$D$21,Portfolio!$H$6:$H$21)</f>
         <v>4433.6000000000004</v>
       </c>
       <c r="N14" s="7"/>
@@ -2929,17 +4332,24 @@
       <c r="AB14" s="6"/>
     </row>
     <row r="15" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="6"/>
       <c r="J15" s="4"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="30">
         <f>M14/K14</f>
-        <v>2.2168000000000001</v>
+        <v>1.7734400000000001</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="30">
         <f>O14/K14</f>
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="P15" s="6"/>
       <c r="R15" s="4"/>
@@ -2955,6 +4365,13 @@
       <c r="AB15" s="6"/>
     </row>
     <row r="16" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="6"/>
       <c r="J16" s="4"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -2974,10 +4391,17 @@
       <c r="AA16" s="5"/>
       <c r="AB16" s="6"/>
     </row>
-    <row r="17" spans="10:28" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="6"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="24" t="s">
-        <v>32</v>
+      <c r="K17" s="51" t="s">
+        <v>29</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
@@ -2996,7 +4420,14 @@
       <c r="AA17" s="5"/>
       <c r="AB17" s="6"/>
     </row>
-    <row r="18" spans="10:28" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="6"/>
       <c r="J18" s="4"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
@@ -3016,14 +4447,21 @@
       <c r="AA18" s="5"/>
       <c r="AB18" s="6"/>
     </row>
-    <row r="19" spans="10:28" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6"/>
       <c r="J19" s="4"/>
       <c r="K19" s="35" t="s">
         <v>14</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="35" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="35" t="s">
@@ -3042,15 +4480,22 @@
       <c r="AA19" s="5"/>
       <c r="AB19" s="6"/>
     </row>
-    <row r="20" spans="10:28" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="6"/>
       <c r="J20" s="4"/>
       <c r="K20" s="22">
         <f>-SUMIF(Transaktionen!$D$6:$D$21,Dashboard!K17,Transaktionen!$G$6:$G$21)</f>
         <v>1000</v>
       </c>
       <c r="L20" s="5"/>
-      <c r="M20" s="37">
-        <f>_xlfn.XLOOKUP(K17,Portfolio!$D$6:$D$21,Portfolio!$F$6:$F$21)*_xlfn.XLOOKUP(K17,Portfolio!$D$6:$D$21,Portfolio!$I$6:$I$21)</f>
+      <c r="M20" s="36">
+        <f>_xlfn.XLOOKUP(K17,Portfolio!$D$6:$D$21,Portfolio!$F$6:$F$21)*_xlfn.XLOOKUP(K17,Portfolio!$D$6:$D$21,Portfolio!$H$6:$H$21)</f>
         <v>951.80000000000007</v>
       </c>
       <c r="N20" s="7"/>
@@ -3071,7 +4516,14 @@
       <c r="AA20" s="5"/>
       <c r="AB20" s="6"/>
     </row>
-    <row r="21" spans="10:28" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B21" s="4"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6"/>
       <c r="J21" s="4"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
@@ -3097,14 +4549,21 @@
       <c r="AA21" s="5"/>
       <c r="AB21" s="6"/>
     </row>
-    <row r="22" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J22" s="4"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="6"/>
+    <row r="22" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="4"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="6"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="10"/>
       <c r="R22" s="4"/>
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
@@ -3117,14 +4576,14 @@
       <c r="AA22" s="5"/>
       <c r="AB22" s="6"/>
     </row>
-    <row r="23" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J23" s="4"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="6"/>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B23" s="4"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6"/>
       <c r="R23" s="4"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
@@ -3137,14 +4596,14 @@
       <c r="AA23" s="5"/>
       <c r="AB23" s="6"/>
     </row>
-    <row r="24" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J24" s="4"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="6"/>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="6"/>
       <c r="R24" s="4"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
@@ -3157,14 +4616,14 @@
       <c r="AA24" s="5"/>
       <c r="AB24" s="6"/>
     </row>
-    <row r="25" spans="10:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J25" s="4"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="6"/>
+    <row r="25" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6"/>
       <c r="R25" s="8"/>
       <c r="S25" s="9"/>
       <c r="T25" s="9"/>
@@ -3177,149 +4636,47 @@
       <c r="AA25" s="9"/>
       <c r="AB25" s="10"/>
     </row>
-    <row r="26" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J26" s="4"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="6"/>
-    </row>
-    <row r="27" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J27" s="4"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="6"/>
-    </row>
-    <row r="28" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J28" s="4"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="6"/>
-    </row>
-    <row r="29" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J29" s="4"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="6"/>
-    </row>
-    <row r="30" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J30" s="4"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="6"/>
-    </row>
-    <row r="31" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J31" s="4"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="6"/>
-    </row>
-    <row r="32" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J32" s="4"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="6"/>
-    </row>
-    <row r="33" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J33" s="4"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="6"/>
-    </row>
-    <row r="34" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J34" s="4"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="6"/>
-    </row>
-    <row r="35" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J35" s="4"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="6"/>
-    </row>
-    <row r="36" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J36" s="4"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="6"/>
-    </row>
-    <row r="37" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J37" s="4"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="6"/>
-    </row>
-    <row r="38" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J38" s="4"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="6"/>
-    </row>
-    <row r="39" spans="10:16" x14ac:dyDescent="0.35">
-      <c r="J39" s="4"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="6"/>
-    </row>
-    <row r="40" spans="10:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J40" s="8"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="10"/>
+    <row r="26" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G7 E7:E8 M9 O9 M15 O15">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+  <conditionalFormatting sqref="M9 M15 M21 E7">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7 O9 O15 O21">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M21 O21">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="M21 M15 M9 E7">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O21 O15 O9 G7">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3331,7 +4688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9625F6F8-4F13-445E-8CC9-F8A284715BAB}">
-  <dimension ref="B1:P22"/>
+  <dimension ref="B1:O22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="2.81640625" customWidth="1"/>
@@ -3339,18 +4696,17 @@
     <col min="4" max="4" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="2.81640625" customWidth="1"/>
-    <col min="13" max="13" width="29.26953125" customWidth="1"/>
-    <col min="14" max="14" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2.81640625" customWidth="1"/>
+    <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="2.81640625" customWidth="1"/>
+    <col min="12" max="12" width="29.26953125" customWidth="1"/>
+    <col min="13" max="13" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3358,35 +4714,33 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="3"/>
-      <c r="L2" s="1"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="4"/>
       <c r="C3" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="6"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="11" t="s">
-        <v>35</v>
-      </c>
+      <c r="I3" s="6"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="5"/>
       <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O3" s="6"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -3394,15 +4748,14 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="6"/>
-      <c r="L4" s="4"/>
+      <c r="I4" s="6"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O4" s="6"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" s="4"/>
       <c r="C5" s="19" t="s">
         <v>9</v>
@@ -3417,64 +4770,63 @@
         <v>3</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="6"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="2:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="M5" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="6"/>
+    </row>
+    <row r="6" spans="2:15" ht="29" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
       <c r="C6" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D6,Transaktionen!$E$6:$E$21)</f>
         <v>10</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="38" t="str">
+      <c r="G6" s="13">
+        <f>IF(F6&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D6,Transaktionen!$G$6:$G$21)/F6),0)</f>
+        <v>100</v>
+      </c>
+      <c r="H6" s="14" t="str">
         <f>'Realtime-Kurse A0NCFR'!B3</f>
         <v>396,76</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="43" t="s">
+      <c r="I6" s="6"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="44">
-        <f>I6*F6</f>
+      <c r="M6" s="41">
+        <f>H6*F6</f>
         <v>3967.6</v>
       </c>
-      <c r="O6" s="45">
-        <f>N6/SUM($N$6:$N$21)</f>
+      <c r="N6" s="42">
+        <f>M6/SUM($M$6:$M$21)</f>
         <v>0.42420613706832033</v>
       </c>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O6" s="6"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="4"/>
       <c r="C7" s="12" t="s">
         <v>10</v>
@@ -3489,340 +4841,368 @@
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D7,Transaktionen!$E$6:$E$21)</f>
         <v>20</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="38" t="str">
+      <c r="G7" s="13">
+        <f>IF(F7&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D7,Transaktionen!$G$6:$G$21)/F7),0)</f>
+        <v>125</v>
+      </c>
+      <c r="H7" s="14" t="str">
         <f>'Realtime-Kurse ETF903'!B3</f>
         <v>221,68</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="12" t="s">
+      <c r="I7" s="6"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="41">
-        <f t="shared" ref="N7:N21" si="0">I7*F7</f>
+      <c r="M7" s="38">
+        <f>H7*F7</f>
         <v>4433.6000000000004</v>
       </c>
-      <c r="O7" s="42">
-        <f t="shared" ref="O7:O21" si="1">N7/SUM($N$6:$N$21)</f>
+      <c r="N7" s="39">
+        <f t="shared" ref="N7:N21" si="0">M7/SUM($M$6:$M$21)</f>
         <v>0.47402972308350266</v>
       </c>
-      <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O7" s="6"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="4"/>
       <c r="C8" s="12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F8" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D8,Transaktionen!$E$6:$E$21)</f>
         <v>10</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="14" t="str">
+      <c r="G8" s="13">
+        <f>IF(F8&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D8,Transaktionen!$G$6:$G$21)/F8),0)</f>
+        <v>100</v>
+      </c>
+      <c r="H8" s="14" t="str">
         <f>'Realtime-Kurse DBX0TR'!B3</f>
         <v>95,18</v>
       </c>
-      <c r="J8" s="6"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="41">
+      <c r="I8" s="6"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="38">
+        <f>H8*F8</f>
+        <v>951.80000000000007</v>
+      </c>
+      <c r="N8" s="39">
         <f t="shared" si="0"/>
-        <v>951.80000000000007</v>
-      </c>
-      <c r="O8" s="42">
-        <f t="shared" si="1"/>
         <v>0.10176413984817706</v>
       </c>
-      <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O8" s="6"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="4"/>
       <c r="C9" s="15"/>
       <c r="F9" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D9,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="6"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="41">
+      <c r="G9" s="13">
+        <f>IF(F9&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D9,Transaktionen!$G$6:$G$21)/F9),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="6"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="38">
+        <f>H9*F9</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O9" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O9" s="6"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="4"/>
       <c r="C10" s="15"/>
       <c r="F10" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D10,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="6"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="41">
+      <c r="G10" s="13">
+        <f>IF(F10&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D10,Transaktionen!$G$6:$G$21)/F10),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="6"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="38">
+        <f>H10*F10</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O10" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O10" s="6"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
       <c r="C11" s="15"/>
       <c r="F11" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D11,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="6"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="41">
+      <c r="G11" s="13">
+        <f>IF(F11&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D11,Transaktionen!$G$6:$G$21)/F11),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="I11" s="6"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="38">
+        <f>H11*F11</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O11" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O11" s="6"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="4"/>
       <c r="C12" s="15"/>
       <c r="F12" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D12,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="6"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="41">
+      <c r="G12" s="13">
+        <f>IF(F12&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D12,Transaktionen!$G$6:$G$21)/F12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="6"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="38">
+        <f>H12*F12</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O12" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O12" s="6"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
       <c r="C13" s="15"/>
       <c r="F13" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D13,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="6"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="41">
+      <c r="G13" s="13">
+        <f>IF(F13&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D13,Transaktionen!$G$6:$G$21)/F13),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="6"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="38">
+        <f>H13*F13</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O13" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="4"/>
       <c r="C14" s="15"/>
       <c r="F14" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D14,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="6"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="41">
+      <c r="G14" s="13">
+        <f>IF(F14&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D14,Transaktionen!$G$6:$G$21)/F14),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="6"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="38">
+        <f>H14*F14</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O14" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O14" s="6"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="4"/>
       <c r="C15" s="15"/>
       <c r="F15" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D15,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="6"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="41">
+      <c r="G15" s="13">
+        <f>IF(F15&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D15,Transaktionen!$G$6:$G$21)/F15),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="I15" s="6"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="38">
+        <f>H15*F15</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O15" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O15" s="6"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="4"/>
       <c r="C16" s="15"/>
       <c r="F16" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D16,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="6"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="41">
+      <c r="G16" s="13">
+        <f>IF(F16&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D16,Transaktionen!$G$6:$G$21)/F16),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="14"/>
+      <c r="I16" s="6"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="38">
+        <f>H16*F16</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O16" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O16" s="6"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="4"/>
       <c r="C17" s="15"/>
       <c r="F17" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D17,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="6"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="41">
+      <c r="G17" s="13">
+        <f>IF(F17&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D17,Transaktionen!$G$6:$G$21)/F17),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="14"/>
+      <c r="I17" s="6"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="38">
+        <f>H17*F17</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O17" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O17" s="6"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="4"/>
       <c r="C18" s="15"/>
       <c r="F18" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D18,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="6"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="41">
+      <c r="G18" s="13">
+        <f>IF(F18&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D18,Transaktionen!$G$6:$G$21)/F18),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="14"/>
+      <c r="I18" s="6"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="38">
+        <f>H18*F18</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O18" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O18" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
       <c r="C19" s="15"/>
       <c r="F19" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D19,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="6"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="41">
+      <c r="G19" s="13">
+        <f>IF(F19&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D19,Transaktionen!$G$6:$G$21)/F19),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="14"/>
+      <c r="I19" s="6"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="38">
+        <f>H19*F19</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O19" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O19" s="6"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="15"/>
       <c r="F20" s="26">
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D20,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="6"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="41">
+      <c r="G20" s="13">
+        <f>IF(F20&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D20,Transaktionen!$G$6:$G$21)/F20),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="6"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="38">
+        <f>H20*F20</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O20" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="O20" s="6"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="4"/>
       <c r="C21" s="16"/>
       <c r="D21" s="17"/>
@@ -3831,23 +5211,25 @@
         <f>SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D21,Transaktionen!$E$6:$E$21)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="6"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="46">
+      <c r="G21" s="48">
+        <f>IF(F21&gt;0,(-SUMIF(Transaktionen!$D$6:$D$21,Portfolio!$D21,Transaktionen!$G$6:$G$21)/F21),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="29"/>
+      <c r="I21" s="6"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="43">
+        <f>H21*F21</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O21" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O21" s="6"/>
+    </row>
+    <row r="22" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="8"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -3855,13 +5237,12 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="10"/>
-      <c r="L22" s="8"/>
+      <c r="I22" s="10"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="9"/>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="10"/>
+      <c r="O22" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4037,11 +5418,11 @@
         <v>10</v>
       </c>
       <c r="F8" s="13">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G8" s="14">
         <f t="shared" si="0"/>
-        <v>-1000</v>
+        <v>-1500</v>
       </c>
       <c r="H8" s="6"/>
       <c r="J8" s="4"/>
@@ -4062,7 +5443,7 @@
         <v>45658</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -4152,7 +5533,7 @@
         <v>46023</v>
       </c>
       <c r="L13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M13" s="28">
         <v>10</v>
@@ -4281,45 +5662,45 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4343,45 +5724,45 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -4404,45 +5785,45 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
